--- a/Lewitus_etal_2014/pbio.1002000.s020.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s020.xlsx
@@ -823,8 +823,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -848,6 +848,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -922,6 +924,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1074,10 +1086,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669086E7-C24A-461F-93CF-8D14D7F9ABEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57230795-2B41-4BA1-BEF3-B072CCE08D53}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C511919F-B355-4FA8-BE39-8F68785C51DA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49FFB015-19C7-4A38-BB38-69BFAACA0625}"/>
 </file>
--- a/Lewitus_etal_2014/pbio.1002000.s020.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s020.xlsx
@@ -823,8 +823,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -848,6 +848,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -922,6 +924,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1075,7 +1087,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669086E7-C24A-461F-93CF-8D14D7F9ABEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4FEB63-CB49-4616-85A8-B2D5184F3DAF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Lewitus_etal_2014/pbio.1002000.s020.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s020.xlsx
@@ -823,8 +823,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -848,6 +848,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -922,6 +924,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1074,10 +1086,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669086E7-C24A-461F-93CF-8D14D7F9ABEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD73E84F-0E17-43DC-8F70-FCF991080CCA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C511919F-B355-4FA8-BE39-8F68785C51DA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ABAB7F1-CE57-4055-8505-6A5F389807C5}"/>
 </file>
--- a/Lewitus_etal_2014/pbio.1002000.s020.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s020.xlsx
@@ -1086,10 +1086,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4FEB63-CB49-4616-85A8-B2D5184F3DAF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C511919F-B355-4FA8-BE39-8F68785C51DA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123CBEEB-55AB-49DC-B8FE-E5B04E05BBCC}"/>
 </file>
--- a/Lewitus_etal_2014/pbio.1002000.s020.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s020.xlsx
@@ -1086,10 +1086,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4FEB63-CB49-4616-85A8-B2D5184F3DAF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C511919F-B355-4FA8-BE39-8F68785C51DA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{588304A9-16D8-4C69-817C-D3D4E2E73115}"/>
 </file>
--- a/Lewitus_etal_2014/pbio.1002000.s020.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s020.xlsx
@@ -1086,10 +1086,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4FEB63-CB49-4616-85A8-B2D5184F3DAF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C511919F-B355-4FA8-BE39-8F68785C51DA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC16A3ED-1BC4-4919-9D89-50D2816018F5}"/>
 </file>